--- a/output/pdf_financials_xlsx/MLP.xlsx
+++ b/output/pdf_financials_xlsx/MLP.xlsx
@@ -3941,22 +3941,22 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.035584</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.5790960000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.110686</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.977478</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.61566</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.201692</v>
       </c>
     </row>
     <row r="93">
@@ -4876,19 +4876,19 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.957843</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.75615</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.060976</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.810245</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-4.290602</v>
       </c>
     </row>
     <row r="119">
@@ -6518,7 +6518,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7174,7 +7178,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -7914,7 +7922,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -8316,7 +8328,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -9058,7 +9074,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -10706,7 +10726,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -12074,7 +12098,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MLP.xlsx
+++ b/output/pdf_financials_xlsx/MLP.xlsx
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000656</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000807</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000878</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001322</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.134477</v>
       </c>
     </row>
     <row r="13">
@@ -1426,16 +1426,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.132578</v>
+        <v>-0.131922</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.049466</v>
+        <v>-0.048659</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.044016</v>
+        <v>-0.043138</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.061024</v>
+        <v>-0.059702</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.108245</v>
@@ -1453,7 +1453,7 @@
         <v>-3.193652</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.921303</v>
+        <v>-6.05578</v>
       </c>
     </row>
     <row r="28">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.132578</v>
+        <v>-0.131922</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.049466</v>
+        <v>-0.048659</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.044016</v>
+        <v>-0.043138</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.061024</v>
+        <v>-0.059702</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.108245</v>
@@ -1527,7 +1527,7 @@
         <v>-3.087777</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.809099</v>
+        <v>-5.943576</v>
       </c>
     </row>
     <row r="30">
@@ -1707,16 +1707,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.798658</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.759961</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.103435</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.629036</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>1.574029</v>
@@ -1781,16 +1781,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.798658</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.759961</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.103435</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.629036</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1.574029</v>
@@ -2225,16 +2225,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.798658</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.931173</v>
+        <v>0.171212</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.173198</v>
+        <v>0.06976300000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.842315</v>
+        <v>1.213279</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.691898</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">

--- a/output/pdf_financials_xlsx/MLP.xlsx
+++ b/output/pdf_financials_xlsx/MLP.xlsx
@@ -2853,22 +2853,22 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.002594</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.06539499999999999</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.08744300000000001</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.364955</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.314859</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.469429</v>
       </c>
     </row>
     <row r="65">
@@ -2952,34 +2952,34 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.049964</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.02998</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.053972</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.06787600000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.212613</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.107948</v>
       </c>
     </row>
     <row r="68">
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.001546</v>
       </c>
     </row>
     <row r="111">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.245614</v>
       </c>
     </row>
     <row r="112">
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.245614</v>
       </c>
     </row>
     <row r="135">
@@ -5553,7 +5553,7 @@
         <v>-1.515795</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.828121</v>
+        <v>-2.073735</v>
       </c>
     </row>
   </sheetData>
@@ -9908,7 +9908,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -10660,7 +10664,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -10926,7 +10934,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -12296,7 +12308,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -13136,7 +13152,11 @@
           <t>Residual value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -13200,7 +13220,11 @@
           <t>Value of finders’ warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -14128,7 +14152,11 @@
           <t>Residual value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -14194,7 +14222,11 @@
           <t>Value of finders’ warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -14912,7 +14944,11 @@
           <t>Shares issued for cash 12,183,000 5,312,260 45,512</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
